--- a/tables/Supplementary_Tables_S1-S5.xlsx
+++ b/tables/Supplementary_Tables_S1-S5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/M2YM4T/DropboxHost/Dropbox/2020/開發/Tt_genomeAssembly2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/M2YM4T/DropboxHost/Dropbox/2020/Paper撰寫/Tt_genomeAssembly2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E929AD16-E77F-174F-ADDF-BBFE3E07E942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D655DE04-1957-E644-AC5B-21371F92E86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="27120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12800" yWindow="2360" windowWidth="34580" windowHeight="22960" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="264">
   <si>
     <t>Workbook description</t>
   </si>
@@ -381,9 +381,6 @@
     <t>FASTA cleaning for orthology search</t>
   </si>
   <si>
-    <t>Removal of . and  prior to EggNOG-mapper</t>
-  </si>
-  <si>
     <t>final_ref/Tt_predicted_proteins.aa.fasta.bak, dorado_polish_gpu1/Tt_predicted_proteins.aa.fasta</t>
   </si>
   <si>
@@ -622,39 +619,15 @@
   </si>
   <si>
     <t>Supplementary Tables S1–S5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Primary-only alignment statistics and residual variant burdens were compared between the round 1 and round 2 polished assemblies to assess whether the second polishing round improved base-level accuracy of the annotation-oriented reference.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Primary-only alignment statistics were obtained from manual samtools flagstat summaries for aln.r1.dorado.primary.bam and aln.r2.dorado.primary.bam.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>High-quality SNP and INDEL counts were derived from dorado_polish_gpu1/p1.var.vcf.gz and dorado_polish_gpu1/p2.var.vcf.gz using QUAL &gt;= 20 and INFO/DP &gt;= 10.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Strict high-confidence INDEL counts were derived using QUAL &gt;= 30 and INFO/DP &gt;= 20.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>INDEL bp indicates the summed absolute length difference |ALT - REF| across filtered INDEL sites.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>These comparisons indicate that round 2 polishing reduced residual SNP and INDEL burdens while leaving overall primary-read mappability essentially unchanged.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>BUSCO and cross-species protein-to-genome mapping were used as complementary evaluations of the polished T. tenax annotation-oriented reference. BUSCO was run on both draft.polish1.bs6.fasta and draft.polish2.bs6.fasta, using either the BUSCO miniprot workflow or MetaEuk. Cross-species homology was assessed by aligning the Trichomonas vaginalis TrichDB v68 annotated proteome to draft.polish2.bs6.fasta with miniprot.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Local BUSCO results show no difference between draft.polish1.bs6.fasta and draft.polish2.bs6.fasta at the summary level, despite the lower residual SNP and INDEL burden observed after round 2 polishing.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -681,7 +654,7 @@
       </rPr>
       <t xml:space="preserve"> predicted proteome</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -704,7 +677,7 @@
       </rPr>
       <t xml:space="preserve"> proteins.</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -727,61 +700,11 @@
       </rPr>
       <t xml:space="preserve"> homology rescue.</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Supplementary Table S4 | Summary of functional annotation layers applied to the</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve"> Trichomonas tenax </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>predicted proteome</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Supplementary Table S3 | Summary of annotation-generation strategy and local outputs for the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>Trichomonas tenax</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve"> polished reference</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Annotation of the polished T. tenax reference was supported by cross-species protein evidence from Trichomonas vaginalis and implemented locally through a GALBA-based structural annotation workflow, followed by sequence extraction and functional annotation merging. A Liftoff-based transfer strategy was recorded as an alternative plan, but no local Liftoff output files were found in the archived workspace copy examined here.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -808,7 +731,7 @@
       </rPr>
       <t xml:space="preserve"> annotation-oriented reference</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -831,7 +754,7 @@
       </rPr>
       <t>assembly.</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -871,11 +794,275 @@
       </rPr>
       <t xml:space="preserve"> genes. It is a reference-centric homology measure, and multiple alignments can map to the same or related genomic loci.</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Supplementary Table S1 | Primary-alignment and residual-variant summary for round 1 and round 2 Dorado polishing of the </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Supplementary tables for the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Trichomonas tenax</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> long-read genome assembly and evidence-guided annotation manuscript.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Supplementary Table S2 | BUSCO and cross-species proteome-mapping summary for evaluation of the</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Trichomonas tenax</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> annotation-oriented reference</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Supplementary Table S3 | Summary of annotation-generation strategy and local outputs for the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Trichomonas tenax </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>polished reference</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Supplementary Table S4 | Summary of functional annotation layers applied to the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Trichomonas tenax</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> predicted proteome</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Supplementary Table S5 | Characterization of the EggNOG-unannotated fraction of the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Trichomonas tenax</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> predicted proteome</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Retained assembly products</t>
+  </si>
+  <si>
+    <t>Structural backbone</t>
+  </si>
+  <si>
+    <t>Assembly FASTA</t>
+  </si>
+  <si>
+    <t>flye_len15k/assembly.fasta</t>
+  </si>
+  <si>
+    <t>Retained for repeat-collapse assessment and exploratory genome-structure analyses</t>
+  </si>
+  <si>
+    <t>Assembly size</t>
+  </si>
+  <si>
+    <t>101.43 Mb</t>
+  </si>
+  <si>
+    <t>Contigs</t>
+  </si>
+  <si>
+    <t>N50</t>
+  </si>
+  <si>
+    <t>924.5 kb</t>
+  </si>
+  <si>
+    <t>Longest contig</t>
+  </si>
+  <si>
+    <t>3.77 Mb</t>
+  </si>
+  <si>
+    <t>Haplotig-reduced draft</t>
+  </si>
+  <si>
+    <t>Polishing input FASTA</t>
+  </si>
+  <si>
+    <t>assembly.no_haplotig.fasta</t>
+  </si>
+  <si>
+    <t>Generated by removing depth-classified haplotig-like contigs</t>
+  </si>
+  <si>
+    <t>99.22 Mb</t>
+  </si>
+  <si>
+    <t>Final annotation-oriented reference</t>
+  </si>
+  <si>
+    <t>draft.polish2.bs6.fasta</t>
+  </si>
+  <si>
+    <t>Two-round Dorado-polished haplotig-reduced reference</t>
+  </si>
+  <si>
+    <t>99.19 Mb</t>
+  </si>
+  <si>
+    <t>939.5 kb</t>
+  </si>
+  <si>
+    <t>Gap bases</t>
+  </si>
+  <si>
+    <t>Depth interpretation</t>
+  </si>
+  <si>
+    <t>Read-depth estimate</t>
+  </si>
+  <si>
+    <t>Representative single-copy depth</t>
+  </si>
+  <si>
+    <t>102.56x</t>
+  </si>
+  <si>
+    <t>Estimated from contig mean-depth distribution after remapping genomic reads</t>
+  </si>
+  <si>
+    <t>Genome-size estimate</t>
+  </si>
+  <si>
+    <t>108.83 Mb</t>
+  </si>
+  <si>
+    <t>Calculated from total basecalled genomic yield divided by representative single-copy depth</t>
+  </si>
+  <si>
+    <t>External comparator</t>
+  </si>
+  <si>
+    <t>Previous flow-cytometry estimate</t>
+  </si>
+  <si>
+    <t>133 ± 4 Mb</t>
+  </si>
+  <si>
+    <t>Dorado polishing</t>
+  </si>
+  <si>
+    <t>The reads ≥15 kb Flye assembly was retained as the structural backbone for repeat-collapse assessment and exploratory genome-structure analyses.</t>
+  </si>
+  <si>
+    <t>The haplotig-reduced draft was generated by removing depth-classified haplotig-like contigs and was used as the polishing input.</t>
+  </si>
+  <si>
+    <t>The final annotation-oriented reference corresponds to the two-round Dorado-polished haplotig-reduced assembly.</t>
+  </si>
+  <si>
+    <t>Primary-only alignment statistics were obtained from manual samtools flagstat summaries for aln.r1.dorado.primary.bam and aln.r2.dorado.primary.bam.</t>
+  </si>
+  <si>
+    <t>High-quality SNP and INDEL counts were derived from dorado_polish_gpu1/p1.var.vcf.gz and dorado_polish_gpu1/p2.var.vcf.gz using QUAL &gt;= 20 and INFO/DP &gt;= 10.</t>
+  </si>
+  <si>
+    <t>Strict high-confidence INDEL counts were derived using QUAL &gt;= 30 and INFO/DP &gt;= 20.</t>
+  </si>
+  <si>
+    <t>INDEL bp indicates the summed absolute length difference |ALT - REF| across filtered INDEL sites.</t>
+  </si>
+  <si>
+    <t>Round 2 polishing reduced residual high-confidence INDEL burden while leaving overall primary-read mappability essentially unchanged.</t>
+  </si>
+  <si>
+    <t>N50, contig length at which 50% of the assembly is contained in contigs of that length or longer.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Reported previously for </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>T. tenax</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Supplementary Table S1 | Retained assembly products, read-depth interpretation, and residual-variant summary for Dorado polishing of the </t>
     </r>
     <r>
       <rPr>
@@ -886,7 +1073,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">Trichomonas tenax </t>
+      <t>Trichomonas tenax</t>
     </r>
     <r>
       <rPr>
@@ -896,18 +1083,19 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>annotation reference</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Supplementary tables for the </t>
+      <t xml:space="preserve"> annotation reference</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Supplementary Table S3 | Summary of annotation-generation strategy and local outputs for the </t>
     </r>
     <r>
       <rPr>
+        <b/>
         <i/>
-        <sz val="11"/>
+        <sz val="14"/>
+        <color rgb="FF1F4E79"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
@@ -915,40 +1103,44 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF1F4E79"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> long-read genome assembly and evidence-guided annotation manuscript.</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Supplementary Table S1 | Primary-alignment and residual-variant summary for round 1 and round 2 Dorado polishing of the </t>
+      <t xml:space="preserve"> polished reference</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Supplementary Table S4 | Summary of functional annotation layers applied to the</t>
     </r>
     <r>
       <rPr>
+        <b/>
         <i/>
-        <sz val="11"/>
+        <sz val="14"/>
+        <color rgb="FF1F4E79"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>Trichomonas tenax</t>
+      <t xml:space="preserve"> Trichomonas tenax </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF1F4E79"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> annotation reference</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Supplementary Table S2 | BUSCO and cross-species proteome-mapping summary for evaluation of the</t>
+      <t>predicted proteome</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Supplementary Table S1 | Retained assembly products, read-depth interpretation, and residual-variant summary for Dorado polishing of the</t>
     </r>
     <r>
       <rPr>
@@ -965,105 +1157,25 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> annotation-oriented reference</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Supplementary Table S3 | Summary of annotation-generation strategy and local outputs for the </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Trichomonas tenax </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>polished reference</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Supplementary Table S4 | Summary of functional annotation layers applied to the </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Trichomonas tenax</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> predicted proteome</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Supplementary Table S5 | Characterization of the EggNOG-unannotated fraction of the </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Trichomonas tenax</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> predicted proteome</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+      <t xml:space="preserve"> annotation reference</t>
+    </r>
+  </si>
+  <si>
+    <t>Retained assembly products, depth-derived genome-size interpretation, primary-only alignment statistics, and residual variant burdens were summarized to document selection of the structural backbone and final annotation-oriented reference.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Removal of problematic characters from FASTA headers before EggNOG-mapper</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="11">
     <font>
       <sz val="11"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF666666"/>
       <name val="Carlito"/>
     </font>
     <font>
@@ -1114,19 +1226,19 @@
       <i/>
       <sz val="14"/>
       <color rgb="FF1F4E79"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="14"/>
-      <color rgb="FF1F4E79"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1150,48 +1262,48 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1364,447 +1476,871 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
-    <col min="2" max="2" width="135.83203125" customWidth="1"/>
+    <col min="2" max="2" width="140.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="20">
-      <c r="A1" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="B1" s="7"/>
+      <c r="A1" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="10"/>
     </row>
     <row r="2" spans="1:2" ht="15">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>217</v>
+      <c r="B2" s="1" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
     </row>
     <row r="6" spans="1:2" ht="15">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>218</v>
+      <c r="B7" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>219</v>
+      <c r="B8" s="1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>220</v>
+      <c r="B9" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>221</v>
+      <c r="B10" s="1" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>222</v>
+      <c r="B11" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="4" width="45" customWidth="1"/>
+    <col min="1" max="1" width="21.83203125" customWidth="1"/>
+    <col min="2" max="3" width="31.33203125" customWidth="1"/>
+    <col min="4" max="4" width="33.1640625" customWidth="1"/>
+    <col min="5" max="5" width="32.33203125" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:11" ht="17.5" customHeight="1">
+      <c r="A1" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+    </row>
+    <row r="2" spans="1:11" ht="27" customHeight="1">
+      <c r="A2" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" s="2" customFormat="1">
+      <c r="A4" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="2" customFormat="1">
+      <c r="A5" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-    </row>
-    <row r="4" spans="1:4" ht="15">
-      <c r="A4" s="10" t="s">
+      <c r="E5" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" s="2" customFormat="1">
+      <c r="A6" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" s="2" customFormat="1">
+      <c r="A7" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D7" s="9">
+        <v>212</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" s="2" customFormat="1">
+      <c r="A8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:11" s="2" customFormat="1">
+      <c r="A9" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+    </row>
+    <row r="10" spans="1:11" s="2" customFormat="1">
+      <c r="A10" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+    </row>
+    <row r="11" spans="1:11" s="2" customFormat="1">
+      <c r="A11" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+    </row>
+    <row r="12" spans="1:11" s="2" customFormat="1">
+      <c r="A12" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D12" s="9">
+        <v>178</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+    </row>
+    <row r="13" spans="1:11" s="2" customFormat="1">
+      <c r="A13" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="6"/>
+    </row>
+    <row r="14" spans="1:11" s="2" customFormat="1">
+      <c r="A14" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+    </row>
+    <row r="15" spans="1:11" s="2" customFormat="1">
+      <c r="A15" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D15" s="9">
+        <v>178</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" s="2" customFormat="1">
+      <c r="A16" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+    </row>
+    <row r="17" spans="1:11" s="2" customFormat="1">
+      <c r="A17" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+    </row>
+    <row r="18" spans="1:11" s="2" customFormat="1">
+      <c r="A18" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="6"/>
+    </row>
+    <row r="19" spans="1:11" s="2" customFormat="1" ht="14" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+    </row>
+    <row r="20" spans="1:11" s="2" customFormat="1" ht="14" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="6"/>
+    </row>
+    <row r="21" spans="1:11" ht="14" customHeight="1"/>
+    <row r="22" spans="1:11" ht="14" customHeight="1">
+      <c r="A22" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="C22" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D22" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E22" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15">
-      <c r="A5" s="8" t="s">
+    <row r="23" spans="1:11" ht="14" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E23" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15">
-      <c r="A6" s="8" t="s">
+    <row r="24" spans="1:11">
+      <c r="A24" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C24" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="E24" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15">
-      <c r="A7" s="8" t="s">
+    <row r="25" spans="1:11">
+      <c r="A25" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C25" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="8">
+      <c r="D25" s="2">
         <v>3726422</v>
       </c>
-      <c r="D7" s="8">
+      <c r="E25" s="2">
         <v>3726422</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15">
-      <c r="A8" s="8" t="s">
+    <row r="26" spans="1:11">
+      <c r="A26" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="8">
+      <c r="D26" s="2">
         <v>3666839</v>
       </c>
-      <c r="D8" s="8">
+      <c r="E26" s="2">
         <v>3666845</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15">
-      <c r="A9" s="8" t="s">
+    <row r="27" spans="1:11">
+      <c r="A27" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="C27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="8">
+      <c r="D27" s="2">
         <v>98.4</v>
       </c>
-      <c r="D9" s="8">
+      <c r="E27" s="2">
         <v>98.4</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15">
-      <c r="A10" s="8" t="s">
+    <row r="28" spans="1:11">
+      <c r="A28" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C28" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="8">
+      <c r="D28" s="2">
         <v>59583</v>
       </c>
-      <c r="D10" s="8">
+      <c r="E28" s="2">
         <v>59577</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15">
-      <c r="A11" s="8" t="s">
+    <row r="29" spans="1:11">
+      <c r="A29" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="C29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="8">
+      <c r="D29" s="2">
         <v>2521</v>
       </c>
-      <c r="D11" s="8">
+      <c r="E29" s="2">
         <v>1811</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15">
-      <c r="A12" s="8" t="s">
+    <row r="30" spans="1:11">
+      <c r="A30" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="C30" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="8">
+      <c r="D30" s="2">
         <v>2667</v>
       </c>
-      <c r="D12" s="8">
+      <c r="E30" s="2">
         <v>2574</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15">
-      <c r="A13" s="8" t="s">
+    <row r="31" spans="1:11">
+      <c r="A31" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="C31" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="8">
+      <c r="D31" s="2">
         <v>34372</v>
       </c>
-      <c r="D13" s="8">
+      <c r="E31" s="2">
         <v>34280</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15">
-      <c r="A14" s="8" t="s">
+    <row r="32" spans="1:11">
+      <c r="A32" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="C32" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="8">
+      <c r="D32" s="2">
         <v>2358</v>
       </c>
-      <c r="D14" s="8">
+      <c r="E32" s="2">
         <v>2306</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15">
-      <c r="A15" s="8" t="s">
+    <row r="33" spans="1:5">
+      <c r="A33" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="C33" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="8">
+      <c r="D33" s="2">
         <v>31295</v>
       </c>
-      <c r="D15" s="8">
+      <c r="E33" s="2">
         <v>26323</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="13" t="s">
+    <row r="36" spans="1:5">
+      <c r="A36" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-    </row>
-    <row r="19" spans="1:4" ht="15">
-      <c r="A19" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-    </row>
-    <row r="20" spans="1:4" ht="15">
-      <c r="A20" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-    </row>
-    <row r="21" spans="1:4" ht="15">
-      <c r="A21" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-    </row>
-    <row r="22" spans="1:4" ht="15">
-      <c r="A22" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-    </row>
-    <row r="23" spans="1:4" ht="15">
-      <c r="A23" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="13" t="s">
+      <c r="B36" s="2"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="2">
+        <v>1</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="2">
+        <v>2</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="2">
+        <v>3</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="2">
+        <v>4</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="2">
+        <v>5</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="2">
+        <v>6</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="2">
+        <v>7</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="2">
+        <v>8</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="2"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-    </row>
-    <row r="26" spans="1:4" ht="15">
-      <c r="A26" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="8" t="s">
+      <c r="B46" s="6"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="2">
+        <v>1</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-    </row>
-    <row r="27" spans="1:4" ht="15">
-      <c r="A27" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="8" t="s">
+      <c r="C47" s="2"/>
+      <c r="D47" s="7"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="2">
+        <v>2</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-    </row>
-    <row r="28" spans="1:4" ht="15">
-      <c r="A28" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="8" t="s">
+      <c r="C48" s="2"/>
+      <c r="D48" s="7"/>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="2">
+        <v>3</v>
+      </c>
+      <c r="B49" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="2">
+        <v>4</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
+  <mergeCells count="9">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="E10:I10"/>
+    <mergeCell ref="E13:J13"/>
+    <mergeCell ref="E18:J18"/>
+    <mergeCell ref="E19:K19"/>
+    <mergeCell ref="E20:J20"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1817,344 +2353,344 @@
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="70" customWidth="1"/>
+    <col min="4" max="4" width="75.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18">
-      <c r="A1" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
+      <c r="A1" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:4" ht="56" customHeight="1">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" ht="15">
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15">
+      <c r="A5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="1">
+        <v>31.8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15">
+      <c r="A6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="1">
+        <v>41</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15">
+      <c r="A7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="1">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15">
+      <c r="A8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="1">
+        <v>52</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15">
+      <c r="A9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="1">
+        <v>31.8</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15">
+      <c r="A10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="1">
+        <v>41</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15">
+      <c r="A11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="1">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15">
+      <c r="A12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="1">
+        <v>52</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15">
+      <c r="A13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="1">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15">
+      <c r="A14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="1">
+        <v>127253</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15">
+      <c r="A15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="1">
+        <v>42983</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15">
+      <c r="A16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="1">
+        <v>59.5</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15">
+      <c r="A17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="1">
+        <v>60058</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15">
+      <c r="A18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="1">
+        <v>61196</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="30">
+      <c r="A19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="1">
+        <v>20521</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15">
+      <c r="A20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.96</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="1:4" ht="15">
+      <c r="A24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+    </row>
+    <row r="25" spans="1:4" ht="15">
+      <c r="A25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+    </row>
+    <row r="26" spans="1:4" ht="15">
+      <c r="A26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-    </row>
-    <row r="4" spans="1:4" ht="15">
-      <c r="A4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15">
-      <c r="A5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="8">
-        <v>31.8</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15">
-      <c r="A6" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="8">
-        <v>41</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15">
-      <c r="A7" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="8">
-        <v>40.299999999999997</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15">
-      <c r="A8" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="8">
-        <v>52</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15">
-      <c r="A9" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="8">
-        <v>31.8</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15">
-      <c r="A10" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="8">
-        <v>41</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15">
-      <c r="A11" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="8">
-        <v>40.299999999999997</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15">
-      <c r="A12" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="8">
-        <v>52</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15">
-      <c r="A13" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="8">
-        <v>40.299999999999997</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15">
-      <c r="A14" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="8">
-        <v>127253</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15">
-      <c r="A15" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="8">
-        <v>42983</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15">
-      <c r="A16" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="8">
-        <v>59.5</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15">
-      <c r="A17" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="8">
-        <v>60058</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15">
-      <c r="A18" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="8">
-        <v>61196</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="30">
-      <c r="A19" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="8">
-        <v>20521</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15">
-      <c r="A20" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="8">
-        <v>2.96</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-    </row>
-    <row r="24" spans="1:4" ht="15">
-      <c r="A24" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="15" t="s">
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+    </row>
+    <row r="27" spans="1:4" ht="15">
+      <c r="A27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-    </row>
-    <row r="25" spans="1:4" ht="15">
-      <c r="A25" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-    </row>
-    <row r="26" spans="1:4" ht="15">
-      <c r="A26" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-    </row>
-    <row r="27" spans="1:4" ht="15">
-      <c r="A27" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
     </row>
     <row r="28" spans="1:4" ht="15">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2166,7 +2702,7 @@
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B27:D27"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2183,22 +2719,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18">
-      <c r="A1" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
+      <c r="A1" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:4" ht="60" customHeight="1">
-      <c r="A2" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="4" spans="1:4" ht="16">
+      <c r="A2" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+    </row>
+    <row r="4" spans="1:4" ht="15">
       <c r="A4" s="3" t="s">
         <v>75</v>
       </c>
@@ -2310,43 +2846,43 @@
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:4">
+      <c r="A14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4" ht="15">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
     </row>
     <row r="16" spans="1:4" ht="15">
       <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
     </row>
     <row r="17" spans="1:4" ht="15">
       <c r="A17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2356,7 +2892,7 @@
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B17:D17"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2373,22 +2909,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18">
-      <c r="A1" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
+      <c r="A1" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:4" ht="50" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="4" spans="1:4" ht="16">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+    </row>
+    <row r="4" spans="1:4" ht="15">
       <c r="A4" s="3" t="s">
         <v>75</v>
       </c>
@@ -2421,171 +2957,171 @@
         <v>117</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15">
       <c r="A7" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="60">
       <c r="A8" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="45">
       <c r="A9" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15">
       <c r="A10" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="45">
       <c r="A11" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15">
       <c r="A12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>101</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15">
       <c r="A13" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>101</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15">
-      <c r="A16" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4" ht="15">
       <c r="A17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
+      <c r="B17" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
     </row>
     <row r="18" spans="1:4" ht="15">
       <c r="A18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
+      <c r="B18" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
     </row>
     <row r="19" spans="1:4" ht="15">
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
+      <c r="B19" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
+      <c r="B20" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2602,406 +3138,406 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="9"/>
+      <c r="A1" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" ht="15">
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="9"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-    </row>
-    <row r="4" spans="1:5" ht="15">
-      <c r="A4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E4" s="9"/>
-    </row>
-    <row r="5" spans="1:5" ht="15">
-      <c r="A5" s="8" t="s">
+      <c r="B5" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="1">
+        <v>33845</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="8">
-        <v>33845</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" ht="15">
+      <c r="A6" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E5" s="9"/>
-    </row>
-    <row r="6" spans="1:5" ht="15">
-      <c r="A6" s="8" t="s">
+      <c r="B6" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="1">
+        <v>19338</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="8">
-        <v>19338</v>
-      </c>
-      <c r="D6" s="8" t="s">
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" ht="15">
+      <c r="A7" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E6" s="9"/>
-    </row>
-    <row r="7" spans="1:5" ht="15">
-      <c r="A7" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="1">
+        <v>14507</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C7" s="8">
-        <v>14507</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" ht="15">
+      <c r="A8" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E7" s="9"/>
-    </row>
-    <row r="8" spans="1:5" ht="15">
-      <c r="A8" s="8" t="s">
+      <c r="B8" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="1">
+        <v>14459</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C8" s="8">
-        <v>14459</v>
-      </c>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" ht="15">
+      <c r="A9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E8" s="9"/>
-    </row>
-    <row r="9" spans="1:5" ht="15">
-      <c r="A9" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="1">
+        <v>10156</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C9" s="8">
-        <v>10156</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" ht="30">
+      <c r="A10" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E9" s="9"/>
-    </row>
-    <row r="10" spans="1:5" ht="30">
-      <c r="A10" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="1">
+        <v>14484</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C10" s="8">
-        <v>14484</v>
-      </c>
-      <c r="D10" s="8" t="s">
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" ht="30">
+      <c r="A11" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E10" s="9"/>
-    </row>
-    <row r="11" spans="1:5" ht="30">
-      <c r="A11" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="B11" s="8" t="s">
+      <c r="C11" s="1">
+        <v>23</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C11" s="8">
-        <v>23</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" ht="30">
+      <c r="A12" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E11" s="9"/>
-    </row>
-    <row r="12" spans="1:5" ht="30">
-      <c r="A12" s="8" t="s">
+      <c r="B12" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="C12" s="1">
+        <v>14201</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" ht="30">
+      <c r="A13" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C12" s="8">
-        <v>14201</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="E12" s="9"/>
-    </row>
-    <row r="13" spans="1:5" ht="30">
-      <c r="A13" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="B13" s="8" t="s">
+      <c r="C13" s="1">
+        <v>259</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C13" s="8">
-        <v>259</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" ht="30">
+      <c r="A14" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E13" s="9"/>
-    </row>
-    <row r="14" spans="1:5" ht="30">
-      <c r="A14" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="B14" s="8" t="s">
+      <c r="C14" s="1">
+        <v>47</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C14" s="8">
-        <v>47</v>
-      </c>
-      <c r="D14" s="8" t="s">
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5" ht="15">
+      <c r="A15" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E14" s="9"/>
-    </row>
-    <row r="15" spans="1:5" ht="15">
-      <c r="A15" s="8" t="s">
+      <c r="B15" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="C15" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" ht="45">
+      <c r="A16" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="E15" s="9"/>
-    </row>
-    <row r="16" spans="1:5" ht="45">
-      <c r="A16" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="B16" s="8" t="s">
+      <c r="C16" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="D16" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" ht="15">
+      <c r="A17" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E16" s="9"/>
-    </row>
-    <row r="17" spans="1:5" ht="15">
-      <c r="A17" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="B17" s="8" t="s">
+      <c r="C17" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="D17" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" ht="30">
+      <c r="A18" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E17" s="9"/>
-    </row>
-    <row r="18" spans="1:5" ht="30">
-      <c r="A18" s="8" t="s">
+      <c r="B18" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="C18" s="1">
+        <v>319</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="8">
-        <v>319</v>
-      </c>
-      <c r="D18" s="8" t="s">
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" ht="15">
+      <c r="A19" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E18" s="9"/>
-    </row>
-    <row r="19" spans="1:5" ht="15">
-      <c r="A19" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="B19" s="8" t="s">
+      <c r="C19" s="1">
+        <v>759</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C19" s="8">
-        <v>759</v>
-      </c>
-      <c r="D19" s="8" t="s">
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" ht="15">
+      <c r="A20" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E19" s="9"/>
-    </row>
-    <row r="20" spans="1:5" ht="15">
-      <c r="A20" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="B20" s="8" t="s">
+      <c r="C20" s="1">
+        <v>1078</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C20" s="8">
-        <v>1078</v>
-      </c>
-      <c r="D20" s="8" t="s">
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" ht="15">
+      <c r="A21" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E20" s="9"/>
-    </row>
-    <row r="21" spans="1:5" ht="15">
-      <c r="A21" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="B21" s="8" t="s">
+      <c r="C21" s="1">
+        <v>22</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C21" s="8">
-        <v>22</v>
-      </c>
-      <c r="D21" s="8" t="s">
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" ht="15">
+      <c r="A22" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E21" s="9"/>
-    </row>
-    <row r="22" spans="1:5" ht="15">
-      <c r="A22" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="B22" s="8" t="s">
+      <c r="C22" s="1">
+        <v>1293</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" ht="15">
+      <c r="A26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C22" s="8">
-        <v>1293</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="E22" s="9"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="9"/>
-    </row>
-    <row r="26" spans="1:5" ht="15">
-      <c r="A26" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="14" t="s">
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" ht="15">
+      <c r="A27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="9"/>
-    </row>
-    <row r="27" spans="1:5" ht="15">
-      <c r="A27" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="14" t="s">
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" ht="15">
+      <c r="A28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="9"/>
-    </row>
-    <row r="28" spans="1:5" ht="15">
-      <c r="A28" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="14" t="s">
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" ht="34" customHeight="1">
+      <c r="A29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="9"/>
-    </row>
-    <row r="29" spans="1:5" ht="34" customHeight="1">
-      <c r="A29" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="9"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>